--- a/data/urban_canopy_visualization.xlsx
+++ b/data/urban_canopy_visualization.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Nkechi Larsen</t>
+          <t xml:space="preserve">Nkechi Larsen </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2023-03-06</t>
+          <t>6/3/2023</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>December 22, 2024</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>11.05.2023</t>
+          <t>11-May-2023</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>Apr 12, 2023</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>15/10/2024</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>November 22, 2023</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>detractor</t>
+          <t xml:space="preserve">detractor </t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>10-04-2024</t>
+          <t>4-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>Aug 21, 2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>02.10.2024</t>
+          <t>2/10/2024</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>January 14, 2023</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>16.12.2024</t>
+          <t>16-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>10-14-2024</t>
+          <t>Oct 14, 2024</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>01-11-2023</t>
+          <t>11/1/2023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
+          <t>February 11, 2023</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>9-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>10-16-2024</t>
+          <t>Oct 16, 2024</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>01-02-2023</t>
+          <t>2/1/2023</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>December 7, 2024</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>12-01-2024</t>
+          <t>1-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>16.04.2023</t>
+          <t>Apr 16, 2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>28/10/2023</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>December 26, 2024</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
+          <t>3-Dec-2023</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>19.10.2024</t>
+          <t>Oct 19, 2024</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>06.12.2023</t>
+          <t>6/12/2023</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>04-18-2023</t>
+          <t>April 18, 2023</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>19-Jul-2023</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>11-09-2024</t>
+          <t>Nov 9, 2024</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>15.10.2024</t>
+          <t>15/10/2024</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>27.05.2023</t>
+          <t>May 27, 2023</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>10-12-2024</t>
+          <t>12-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>Dec 14, 2023</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>08.11.2024</t>
+          <t>8/11/2024</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>12-27-2024</t>
+          <t>December 27, 2024</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>11-04-2024</t>
+          <t>4-Nov-2024</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>15.11.2023</t>
+          <t>Nov 15, 2023</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
       <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>5/10/2024</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>01.01.2023</t>
+          <t>January 1, 2023</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>08.04.2023</t>
+          <t>8-Apr-2023</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>Oct 27, 2024</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>8/2/2023</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>October 26, 2024</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>21-Nov-2024</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>11.12.2024</t>
+          <t>Dec 11, 2024</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>21.07.2023</t>
+          <t>21/7/2023</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>2023-03-03</t>
+          <t>March 3, 2023</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>10-08-2024</t>
+          <t>8-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>03-23-2023</t>
+          <t>Mar 23, 2023</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>20/11/2024</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>12-12-2024</t>
+          <t>December 12, 2024</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>11-09-2024</t>
+          <t>9-Nov-2024</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>Oct 27, 2023</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>12-14-2024</t>
+          <t>14/12/2024</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>12-06-2024</t>
+          <t>December 6, 2024</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>02-01-2023</t>
+          <t>1-Feb-2023</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3911,7 +3911,7 @@
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>10-12-2024</t>
+          <t>Oct 12, 2024</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>08-06-2023</t>
+          <t>6/8/2023</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>December 1, 2024</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>12-24-2024</t>
+          <t>24-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>05-23-2023</t>
+          <t>May 23, 2023</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>24/10/2024</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>October 28, 2024</t>
         </is>
       </c>
     </row>

--- a/data/urban_canopy_visualization.xlsx
+++ b/data/urban_canopy_visualization.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>24 Aug 2023</t>
+          <t>24/8/2023</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2024</t>
+          <t>28-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>14/12/2023</t>
+          <t>14 Dec 2023</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>8 Nov 2024</t>
+          <t>8.11.2024</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>6/3/2023</t>
+          <t>6-3-2023</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>December 22, 2024</t>
+          <t>22 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>11-May-2023</t>
+          <t>11/5/2023</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>9 Nov 2024</t>
+          <t>9-Nov-2024</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Apr 12, 2023</t>
+          <t>12 Apr 2023</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>15.10.2024</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>November 22, 2023</t>
+          <t>22-11-2023</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>4-Oct-2024</t>
+          <t>4 Oct, 2024</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>13/01/2023</t>
+          <t>13/1/2023</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>December 26, 2024</t>
+          <t>26-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Aug 21, 2023</t>
+          <t>21 Aug 2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>November 13, 2024</t>
+          <t>13.11.2024</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>June 25, 2023</t>
+          <t>25-6-2023</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2/10/2024</t>
+          <t>2 Oct, 2024</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>December 21, 2023</t>
+          <t>21/12/2023</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>December 2, 2024</t>
+          <t>2-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>January 14, 2023</t>
+          <t>14 Jan 2023</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>17 Nov 2024</t>
+          <t>17.11.2024</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>17 Dec 2023</t>
+          <t>17-12-2023</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>16-Dec-2024</t>
+          <t>16 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>04/11/2024</t>
+          <t>4-Nov-2024</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>March 28, 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Oct 14, 2024</t>
+          <t>14.10.2024</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>20 Apr 2023</t>
+          <t>20-4-2023</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>24/11/2024</t>
+          <t>24 Nov, 2024</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>09/10/2024</t>
+          <t>9-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>February 11, 2023</t>
+          <t>11 Feb 2023</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>9-Oct-2024</t>
+          <t>9.10.2024</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>18 May 2023</t>
+          <t>18-5-2023</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1556,7 +1556,7 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Oct 16, 2024</t>
+          <t>16 Oct, 2024</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>December 7, 2024</t>
+          <t>7-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>November 9, 2023</t>
+          <t>9 Nov 2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>6 Oct 2024</t>
+          <t>6.10.2024</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>January 27, 2023</t>
+          <t>27-1-2023</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>1-Dec-2024</t>
+          <t>1 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Apr 16, 2023</t>
+          <t>16/4/2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>December 1, 2024</t>
+          <t>1-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>28/10/2023</t>
+          <t>28 Oct 2023</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>December 17, 2024</t>
+          <t>17.12.2024</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>17/06/2023</t>
+          <t>17-6-2023</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>18/12/2024</t>
+          <t>18 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>14/08/2023</t>
+          <t>14/8/2023</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>December 26, 2024</t>
+          <t>26-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>3-Dec-2023</t>
+          <t>3 Dec 2023</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
+          <t>17.11.2024</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>June 21, 2023</t>
+          <t>21-6-2023</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>28 Nov 2024</t>
+          <t>28 Nov, 2024</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>July 17, 2023</t>
+          <t>17/7/2023</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Oct 19, 2024</t>
+          <t>19-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>June 7, 2023</t>
+          <t>7 Jun 2023</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2024</t>
+          <t>17.10.2024</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>April 16, 2023</t>
+          <t>16-4-2023</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>11 Nov, 2024</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>April 16, 2023</t>
+          <t>16/4/2023</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>11-Nov-2024</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>6/12/2023</t>
+          <t>6 Dec 2023</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>18/10/2024</t>
+          <t>18.10.2024</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>April 18, 2023</t>
+          <t>18-4-2023</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>21 Nov 2024</t>
+          <t>21 Nov, 2024</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>September 13, 2023</t>
+          <t>13/9/2023</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>26 Nov 2024</t>
+          <t>26-Nov-2024</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>19-Jul-2023</t>
+          <t>19 Jul 2023</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Nov 9, 2024</t>
+          <t>9.11.2024</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>21/05/2023</t>
+          <t>21-5-2023</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>15 Oct, 2024</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>May 27, 2023</t>
+          <t>27/5/2023</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Dec 14, 2023</t>
+          <t>14 Dec 2023</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>8/11/2024</t>
+          <t>8.11.2024</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>June 19, 2023</t>
+          <t>19-6-2023</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>December 27, 2024</t>
+          <t>27 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>07/03/2023</t>
+          <t>7/3/2023</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>July 27, 2023</t>
+          <t>27 Jul 2023</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>October 11, 2024</t>
+          <t>11.10.2024</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Nov 15, 2023</t>
+          <t>15-11-2023</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
       <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>5/10/2024</t>
+          <t>5 Oct, 2024</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>November 3, 2023</t>
+          <t>3/11/2023</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>14/12/2024</t>
+          <t>14-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>January 1, 2023</t>
+          <t>1 Jan 2023</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>17/10/2024</t>
+          <t>17.10.2024</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>22/02/2023</t>
+          <t>22-2-2023</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>December 15, 2024</t>
+          <t>15 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>8-Apr-2023</t>
+          <t>8/4/2023</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Oct 27, 2024</t>
+          <t>27-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>8/2/2023</t>
+          <t>8 Feb 2023</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>October 26, 2024</t>
+          <t>26.10.2024</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>4 May 2023</t>
+          <t>4-5-2023</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>21-Nov-2024</t>
+          <t>21 Nov, 2024</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>20/01/2023</t>
+          <t>20/1/2023</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Dec 11, 2024</t>
+          <t>11-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>21/7/2023</t>
+          <t>21 Jul 2023</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>07/11/2024</t>
+          <t>7.11.2024</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>March 3, 2023</t>
+          <t>3-3-2023</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3365,7 +3365,7 @@
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>December 23, 2024</t>
+          <t>23 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>14 Aug 2023</t>
+          <t>14/8/2023</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Mar 23, 2023</t>
+          <t>23 Mar 2023</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>20/11/2024</t>
+          <t>20.11.2024</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>12 Dec 2023</t>
+          <t>12-12-2023</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>December 12, 2024</t>
+          <t>12 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>04/01/2023</t>
+          <t>4/1/2023</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2024</t>
+          <t>27-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>04/01/2023</t>
+          <t>4 Jan 2023</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>27 Oct 2024</t>
+          <t>27.10.2024</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>March 9, 2023</t>
+          <t>9-3-2023</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>9-Nov-2024</t>
+          <t>9 Nov, 2024</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Oct 27, 2023</t>
+          <t>27/10/2023</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>14/12/2024</t>
+          <t>14-Dec-2024</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>25/05/2023</t>
+          <t>25 May 2023</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>December 6, 2024</t>
+          <t>6.12.2024</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1-Feb-2023</t>
+          <t>1-2-2023</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3858,7 +3858,7 @@
       <c r="J62" s="4" t="inlineStr"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>16/11/2024</t>
+          <t>16 Nov, 2024</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>December 11, 2023</t>
+          <t>11/12/2023</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3911,7 +3911,7 @@
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>Oct 12, 2024</t>
+          <t>12-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>6/8/2023</t>
+          <t>6 Aug 2023</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>December 4, 2024</t>
+          <t>4.12.2024</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>February 26, 2023</t>
+          <t>26-2-2023</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>December 1, 2024</t>
+          <t>1 Dec, 2024</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>24 Jun 2023</t>
+          <t>24/6/2023</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>October 19, 2024</t>
+          <t>19.10.2024</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>May 23, 2023</t>
+          <t>23-5-2023</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>24 Oct, 2024</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>February 17, 2023</t>
+          <t>17/2/2023</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>October 28, 2024</t>
+          <t>28-Oct-2024</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>October 28, 2024</t>
+          <t>28.10.2024</t>
         </is>
       </c>
     </row>
